--- a/reference/origins/product info/WA_Edibles_By_Brand_Final_Curated_Normalized.xlsx
+++ b/reference/origins/product info/WA_Edibles_By_Brand_Final_Curated_Normalized.xlsx
@@ -679,7 +679,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -807,7 +807,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2797,7 +2797,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Constellation Cannabis</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
